--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -612,23 +612,46 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -643,10 +666,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -682,16 +705,29 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>2</v>
+      <c r="B4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -716,14 +752,14 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -733,19 +769,19 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="23" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="24" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -756,7 +792,7 @@
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
     <col width="16" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
@@ -1079,10 +1115,8 @@
           <t>Upana Rai</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9804320034</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9804320034</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1097,10 +1131,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9804320034</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9804320034</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -1117,10 +1149,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.672023</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.672023</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1176,25 +1206,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L12-5</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.348141</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.348141</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1295,10 +1321,8 @@
           <t>Sabin Shahi</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9803974909</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9803974909</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1313,10 +1337,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9803974909</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9803974909</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1333,10 +1355,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.70056</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.70056</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1392,53 +1412,265 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L56-3</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.3791</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.37909999999999</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>14h 43m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:35 PM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter Faulty   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Router / Adapter Faulty</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347459</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi lama</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi lama</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9818142839</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:35:30 PM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9818142839</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 04:08:10 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:35:30 PM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.687254</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Madhyapur Thimi, Near by Nagarpalika, Rai - Madhyapur Thimi Municipality, Bhaktapur, Bagmati, Centra</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>laxmilama22@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>03:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L20-5</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.389687</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter Faulty   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>14h 43m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>20h 27m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX3" s="3" t="inlineStr">
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router / Adapter Faulty   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -787,7 +787,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1527,10 +1527,8 @@
           <t>Laxmi lama</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9818142839</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9818142839</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1545,10 +1543,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9818142839</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9818142839</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1565,10 +1561,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.687254</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.687254</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1624,25 +1618,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>L20-5</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.389687</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.389687</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : Router / Adapter Faulty   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,36 +528,72 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="B5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -616,19 +652,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -639,19 +675,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -666,12 +702,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -682,10 +720,20 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -698,10 +746,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -711,23 +765,54 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>3</v>
+      <c r="E5" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -741,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -754,43 +839,43 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="28" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="24" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
+    <col width="21" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="16" customWidth="1" min="50" max="50"/>
@@ -1666,6 +1751,1062 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 1:11 PM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Replacemengt  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Router Replacemengt</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346177</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>kajal shrestha</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>kajal shrestha</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9803332252</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 02:56:01 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>CHB9803332252</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 02:56:01 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 01:11:30 PM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Pani pokhari , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>Kajalshrestha@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Hareram Pandit</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L59-2</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Replacemengt  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 15m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 15m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Replacemengt  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 1:00 PM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router instal   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 router instal</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347295</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Gadesh kumar malla</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Gadesh kumar malla</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9849804034</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 01:00:25 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>BKT9849804035</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:36:30 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 01:00:25 PM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Thimi, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>9849804034@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>06:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L43-3</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router instal   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>23h 23m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 router instal   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 1:14 PM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347643</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Abhishek Pokharel</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Abhishek Pokharel</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9851339262</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 01:14:33 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9851339262</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 07:31:42 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 01:14:33 PM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.71364</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Near Dibya Hospitality Pvt. Ltd.,Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>abhishekpokharel100@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>00:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L30-3</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.36408</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>17h 42m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 1:09 PM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347450</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Jay Pratap Maskey</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Jay Pratap Maskey</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9840402777</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 01:09:09 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9840402777</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 04:01:16 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 01:09:09 PM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Park N Wash, P996+MCR, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L33-1</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>21h 7m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 1:06 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347381</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Bedhari Chaulagain</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Bedhari Chaulagain</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9841121967</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 01:13:33 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9841121967</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 02:57:55 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 01:13:33 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.71799</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>customer experience sales</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>27.718545021852147, 85.3536778372342, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>chaulagaintara95@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>01:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L2-8</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.35404</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>22h 15m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -872,7 +872,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1818,10 +1818,8 @@
           <t>kajal shrestha</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9803332252</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9803332252</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1856,10 +1854,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1911,25 +1907,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L59-2</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Replacemengt  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -2030,10 +2022,8 @@
           <t>Gadesh kumar malla</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9849804034</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9849804034</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2123,10 +2113,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -2137,7 +2125,7 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 router instal   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -2238,10 +2226,8 @@
           <t>Abhishek Pokharel</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9851339262</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9851339262</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2276,10 +2262,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.71364</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.71364</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -2335,25 +2319,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>L30-3</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.36408</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.36408</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2454,10 +2434,8 @@
           <t>Jay Pratap Maskey</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9840402777</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9840402777</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2525,10 +2503,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH8" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH8" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI8" s="3" t="inlineStr"/>
       <c r="AJ8" s="3" t="inlineStr"/>
@@ -2543,10 +2519,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
@@ -2557,7 +2531,7 @@
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2658,10 +2632,8 @@
           <t>Bedhari Chaulagain</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9841121967</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9841121967</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2696,10 +2668,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.71799</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.71799</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2755,25 +2725,21 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>L2-8</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.35404</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.35404</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
@@ -755,7 +755,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>4</v>
@@ -812,7 +812,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -826,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX9"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -872,7 +872,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2773,6 +2773,210 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 1:29 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343902</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Mira Giri</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Mira Giri</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9813940809</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:25:58 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9813940809</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:25:58 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 01:29:21 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Jana Marg 2 Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>9813940809@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 3m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 3m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -872,7 +872,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2840,10 +2840,8 @@
           <t>Mira Giri</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9813940809</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9813940809</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2929,10 +2927,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -2943,7 +2939,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -568,32 +568,50 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>55.6%</t>
+      <c r="B6" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -652,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
@@ -675,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -702,14 +720,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,6 +754,11 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -752,67 +776,123 @@
         <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>9</v>
+      <c r="E7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -826,13 +906,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AX14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -867,18 +947,18 @@
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="22" customWidth="1" min="38" max="38"/>
-    <col width="21" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="16" customWidth="1" min="50" max="50"/>
+    <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2973,6 +3053,734 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 1:53 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345243</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Mina Basnet</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Mina Basnet</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9744405507</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 01:53:45 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>KLK9744405507</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 07:10:49 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 01:53:45 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Near by Navajeevan International (p.) ltd. - Employment agency P8V9+PQQ Kathmandu 44600, Kathmandu,</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>9744405507@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>20:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>4,16</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>2d 18h 42m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 1:56 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346175</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Khatri</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Khatri</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9702617283</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 01:56:17 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>BKT9702617283</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 02:54:33 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 01:56:17 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Suryabinayak Chowk near Ganesh mandir , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>9861283872@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>15:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 1m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 2:00 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr"/>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 1:48 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343733</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Bohora</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Bohora</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9851422020</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 05:00:11 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>LTP9851422020</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:12:06 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:00:59 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Imadol, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>9851422020@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB322</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>4d 48m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>7</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -682,30 +682,53 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>6.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B4" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>69.2%</t>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -720,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -773,35 +796,35 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-STB App not working</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>1</v>
@@ -810,20 +833,20 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>1</v>
@@ -832,14 +855,14 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -854,14 +877,14 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
@@ -874,25 +897,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" s="4" t="n">
+      <c r="C8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>13</v>
+      <c r="E8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -906,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX14"/>
+  <dimension ref="A1:AX17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -933,7 +978,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="28" customWidth="1" min="28" max="28"/>
@@ -950,7 +995,7 @@
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
     <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
@@ -3120,10 +3165,8 @@
           <t>Mina Basnet</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9744405507</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9744405507</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3213,10 +3256,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
@@ -3227,7 +3268,7 @@
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -3328,10 +3369,8 @@
           <t>Kamal Khatri</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9702617283</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9702617283</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3421,10 +3460,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
@@ -3435,7 +3472,7 @@
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow internet   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3644,10 +3681,8 @@
           <t>Ramesh Bohora</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9851422020</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9851422020</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3733,10 +3768,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
@@ -3747,35 +3780,663 @@
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>4d 48m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>1d 21h</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>4d 48m</t>
-        </is>
-      </c>
-      <c r="AU14" s="3" t="inlineStr">
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 2:06 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : tv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>tv issue</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344541</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>prakash panday</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>prakash panday</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9865499752</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:06:07 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>BKT9865499752</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:52:31 AM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:06:07 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.705516762161928</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>suryabanyak , Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>abcde@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-STB App not working</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.32394409179689</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : tv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>3d 4h 13m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : tv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 2:03 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344890</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Timilsina</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Timilsina</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9851326768</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:15:57 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9866486431</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 02:16:43 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:15:57 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.679234</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>customer experience sales</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Near Chokha Binayak Sthan, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>timilsinakrish@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Rikesh Shrestha</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L16-1</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.444639</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 59m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 2:03 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344769</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Ranjeet Shah</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Ranjeet Shah</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9702319732</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:26:24 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>LTP9702319732</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:26:24 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:03:11 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>27.656991599645185,85.33656510649075, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>97023197321@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>CDB042</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 36m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 36m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV14" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW14" s="3" t="inlineStr">
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX14" s="3" t="inlineStr">
+      <c r="AX17" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>7</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.6%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX17"/>
+  <dimension ref="A1:AX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -978,7 +978,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="28" customWidth="1" min="28" max="28"/>
@@ -997,7 +997,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3881,10 +3881,8 @@
           <t>prakash panday</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9865499752</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9865499752</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3919,10 +3917,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.705516762161928</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.70551676216193</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3974,25 +3970,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>1,1</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.32394409179689</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.32394409179689</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : tv issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -4093,10 +4085,8 @@
           <t>Bijay Timilsina</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9851326768</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9851326768</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4131,10 +4121,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.679234</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.679234</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -4186,25 +4174,21 @@
           <t>Rikesh Shrestha</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>L16-1</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.444639</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.444639</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -4305,10 +4289,8 @@
           <t>Ranjeet Shah</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9702319732</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9702319732</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4394,10 +4376,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -4408,29 +4388,29 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 36m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 36m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>3d 1h 36m</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>3d 1h 36m</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -4439,6 +4419,222 @@
       <c r="AX17" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 2:28 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr"/>
+      <c r="V18" s="3" t="inlineStr"/>
+      <c r="W18" s="3" t="inlineStr"/>
+      <c r="X18" s="3" t="inlineStr"/>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr"/>
+      <c r="AA18" s="3" t="inlineStr"/>
+      <c r="AB18" s="3" t="inlineStr"/>
+      <c r="AC18" s="3" t="inlineStr"/>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr"/>
+      <c r="AF18" s="3" t="inlineStr"/>
+      <c r="AG18" s="3" t="inlineStr"/>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr"/>
+      <c r="AM18" s="3" t="inlineStr"/>
+      <c r="AN18" s="3" t="inlineStr"/>
+      <c r="AO18" s="3" t="inlineStr"/>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 2:29 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr"/>
+      <c r="V19" s="3" t="inlineStr"/>
+      <c r="W19" s="3" t="inlineStr"/>
+      <c r="X19" s="3" t="inlineStr"/>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr"/>
+      <c r="AA19" s="3" t="inlineStr"/>
+      <c r="AB19" s="3" t="inlineStr"/>
+      <c r="AC19" s="3" t="inlineStr"/>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AM19" s="3" t="inlineStr"/>
+      <c r="AN19" s="3" t="inlineStr"/>
+      <c r="AO19" s="3" t="inlineStr"/>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>7</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>36.8%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>21.1%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX19"/>
+  <dimension ref="A1:AX20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -997,7 +997,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4638,6 +4638,218 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 2:31 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Replacemengt  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Router Replacemengt</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346177</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>kajal shrestha</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>kajal shrestha</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9803332252</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:31:49 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>CHB9803332252</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 02:56:01 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:31:49 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Pani pokhari , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>Kajalshrestha@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Hareram Pandit</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L59-2</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Replacemengt  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 35m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Replacemengt  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -546,72 +546,90 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B7" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>36.8%</t>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>30.4%</t>
         </is>
       </c>
     </row>
@@ -682,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>17.4%</t>
         </is>
       </c>
     </row>
@@ -705,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
     </row>
@@ -728,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -951,7 +969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX20"/>
+  <dimension ref="A1:AX24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -997,7 +1015,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4705,10 +4723,8 @@
           <t>kajal shrestha</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9803332252</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9803332252</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4743,10 +4759,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -4798,47 +4812,43 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>L59-2</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 35m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Replacemengt  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS20" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 35m</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Replacemengt  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -4847,6 +4857,438 @@
       <c r="AX20" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 2:49 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr"/>
+      <c r="V21" s="3" t="inlineStr"/>
+      <c r="W21" s="3" t="inlineStr"/>
+      <c r="X21" s="3" t="inlineStr"/>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr"/>
+      <c r="AA21" s="3" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr"/>
+      <c r="AC21" s="3" t="inlineStr"/>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr"/>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr"/>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr"/>
+      <c r="AM21" s="3" t="inlineStr"/>
+      <c r="AN21" s="3" t="inlineStr"/>
+      <c r="AO21" s="3" t="inlineStr"/>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 2:51 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr"/>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr"/>
+      <c r="V22" s="3" t="inlineStr"/>
+      <c r="W22" s="3" t="inlineStr"/>
+      <c r="X22" s="3" t="inlineStr"/>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr"/>
+      <c r="AA22" s="3" t="inlineStr"/>
+      <c r="AB22" s="3" t="inlineStr"/>
+      <c r="AC22" s="3" t="inlineStr"/>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr"/>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr"/>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr"/>
+      <c r="AM22" s="3" t="inlineStr"/>
+      <c r="AN22" s="3" t="inlineStr"/>
+      <c r="AO22" s="3" t="inlineStr"/>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 2:54 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr"/>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr"/>
+      <c r="X23" s="3" t="inlineStr"/>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr"/>
+      <c r="AA23" s="3" t="inlineStr"/>
+      <c r="AB23" s="3" t="inlineStr"/>
+      <c r="AC23" s="3" t="inlineStr"/>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr"/>
+      <c r="AF23" s="3" t="inlineStr"/>
+      <c r="AG23" s="3" t="inlineStr"/>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr"/>
+      <c r="AM23" s="3" t="inlineStr"/>
+      <c r="AN23" s="3" t="inlineStr"/>
+      <c r="AO23" s="3" t="inlineStr"/>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 2:50 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr"/>
+      <c r="V24" s="3" t="inlineStr"/>
+      <c r="W24" s="3" t="inlineStr"/>
+      <c r="X24" s="3" t="inlineStr"/>
+      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="inlineStr"/>
+      <c r="AA24" s="3" t="inlineStr"/>
+      <c r="AB24" s="3" t="inlineStr"/>
+      <c r="AC24" s="3" t="inlineStr"/>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr"/>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr"/>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr"/>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr"/>
+      <c r="AM24" s="3" t="inlineStr"/>
+      <c r="AN24" s="3" t="inlineStr"/>
+      <c r="AO24" s="3" t="inlineStr"/>
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>41.4%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.2%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>55.2%</t>
         </is>
       </c>
     </row>
@@ -761,15 +761,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -785,20 +786,25 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -814,16 +820,19 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -836,22 +845,25 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -866,21 +878,24 @@
       <c r="E4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -888,43 +903,49 @@
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -932,30 +953,61 @@
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>16</v>
+      <c r="G9" s="4" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -969,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX24"/>
+  <dimension ref="A1:AX30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -980,14 +1032,14 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="31" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -997,14 +1049,14 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="28" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="32" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -1015,7 +1067,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5292,6 +5344,1266 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 3:40 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344007</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Avash Shrestha</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Avash Shrestha</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9843768014</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:40:33 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9843768014</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:47:22 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:40:33 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur Patna	Agnisala, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr"/>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>09:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>3,16</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 53m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 3:12 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346022</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Kapil Yadav</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Kapil Yadav</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9861880571</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:12:04 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9861880571</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 01:01:11 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:12:04 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.680783</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Madhyapur Thimi near Anup Store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>kplyadav198@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>16:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>4,13</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.366294</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 10m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 3:18 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345013</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Ram Krishna BK</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Ram Krishna BK</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9803039488</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:18:40 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9841703959</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 04:07:58 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:18:40 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.661198</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Near Imadol Krishna Mandir, Mahalaxmi, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr"/>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>23:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>CDB181</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.343105</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 10m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 3:12 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347853</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Sumit Waiba Tamang</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Sumit Waiba Tamang</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9840851111</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:12:24 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>CHB9840851666</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 07:42:40 AM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:12:24 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>T.U. Teaching Hospital T.U. Teaching Hospital - University hospital Maharajgunj Sadak Kathmandu 4460</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>9840851666@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>L36-4</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>7h 29m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 3:09 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347066</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Sushila Dhakal</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Sushila Dhakal</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9860711779</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:09:44 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9860711779</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:02:47 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:09:44 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.74559</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>near Peaceland Academy, Manamaiju, P8V5+WVH, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>08:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>L29-4</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.3097</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 6m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 3:04 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : frquently disconnected issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>frquently disconnected issue</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342620</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Neupane</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Neupane</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9847329472</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:04:19 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>KLK9816451459</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 03:57:23 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:04:19 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>QFX Cinemas, City Square Mall QFX Cinemas, City Square Mall - Movie theater P8P9+549 ???????? ??????</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>9816451459@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Due to Optical Power flapping</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>20:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>L55-1</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : frquently disconnected issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>4d 23h 6m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : frquently disconnected issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -616,20 +616,38 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>41.4%</t>
+      <c r="B8" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>45.2%</t>
         </is>
       </c>
     </row>
@@ -700,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.1%</t>
         </is>
       </c>
     </row>
@@ -711,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>6.5%</t>
         </is>
       </c>
     </row>
@@ -734,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
     </row>
@@ -761,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -770,7 +788,8 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -806,6 +825,11 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -823,7 +847,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>6</v>
@@ -831,14 +855,17 @@
       <c r="F2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G2" s="6" t="n">
-        <v>16</v>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>NETTV-STB App not working</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -848,22 +875,25 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>NETTV-STB App not working</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -873,22 +903,25 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -904,16 +937,19 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -923,32 +959,35 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -956,24 +995,27 @@
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -981,33 +1023,67 @@
       <c r="F8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E9" s="4" t="n">
+      <c r="D10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>22</v>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX30"/>
+  <dimension ref="A1:AX32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1034,10 +1110,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="31" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1061,7 +1137,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="22" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -5411,10 +5487,8 @@
           <t>Avash Shrestha</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9843768014</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9843768014</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5500,10 +5574,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
@@ -5514,7 +5586,7 @@
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -5615,10 +5687,8 @@
           <t>Kapil Yadav</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9861880571</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9861880571</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5653,10 +5723,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.680783</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.680783</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -5712,25 +5780,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>4,13</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.366294</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.366294</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -5831,10 +5895,8 @@
           <t>Ram Krishna BK</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9803039488</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9803039488</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5869,10 +5931,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.661198</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.661198</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -5924,25 +5984,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>CDB181</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.343105</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.34310499999999</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -6043,10 +6099,8 @@
           <t>Sumit Waiba Tamang</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9840851111</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9840851111</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -6132,10 +6186,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
@@ -6146,7 +6198,7 @@
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -6247,10 +6299,8 @@
           <t>Sushila Dhakal</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9860711779</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9860711779</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6285,10 +6335,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.74559</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.74559</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -6344,25 +6392,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>L29-4</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.3097</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.30970000000001</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -6463,10 +6507,8 @@
           <t>Prakash Neupane</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9847329472</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9847329472</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6556,10 +6598,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -6570,37 +6610,465 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>4d 23h 6m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
           <t>Case : frquently disconnected issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS30" s="3" t="inlineStr">
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 3:56 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348122</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Gayatri Basnet</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Gayatri Basnet</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9863746918</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:56:05 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9863746918</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 10:42:46 AM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:56:05 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.704289</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Kageshwori Manohara 44600 near by Amar Singh Chowk , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>durgabasnet9860@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>L24-8</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.384447</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT30" s="3" t="inlineStr">
-        <is>
-          <t>4d 23h 6m</t>
-        </is>
-      </c>
-      <c r="AU30" s="3" t="inlineStr">
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>5h 13m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV30" s="3" t="inlineStr">
-        <is>
-          <t>Case : frquently disconnected issue  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW30" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX30" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 3:57 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>iptv setbox issue</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345845</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Manju Kumari Sharma</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Manju Kumari Sharma</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9841775966</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:57:09 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9841775966</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:08:15 AM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:57:49 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.721333</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Thulo Bharyang, Nagarjun ward no:3,near Mina Dairy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr"/>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>18:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.281632</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>2d 4h 49m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>17.1%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -875,25 +875,25 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>NETTV-STB App not working</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -903,10 +903,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -977,7 +977,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>NETTV-STB App not working</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -1005,17 +1005,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -1033,17 +1033,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -1080,10 +1080,10 @@
         <v>4</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX32"/>
+  <dimension ref="A1:AX36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1110,10 +1110,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="31" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -6711,10 +6711,8 @@
           <t>Gayatri Basnet</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9863746918</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9863746918</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6749,10 +6747,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>27.704289</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>27.704289</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -6808,25 +6804,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>L24-8</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.384447</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.38444699999999</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -6927,10 +6919,8 @@
           <t>Manju Kumari Sharma</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9841775966</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9841775966</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6965,10 +6955,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.721333</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.721333</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -7020,53 +7008,893 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.281632</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.281632</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>2d 4h 49m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv setbox issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS32" s="3" t="inlineStr">
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 4:02 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343733</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Bohora</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Bohora</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9851422020</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 04:02:09 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>LTP9851422020</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 01:12:06 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 04:02:09 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Imadol, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>9851422020@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>12:48 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>CDB322</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>2d 4h 49m</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>4d 2h 50m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV32" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv setbox issue  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW32" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX32" s="3" t="inlineStr">
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 4:04 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343902</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Mira Giri</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Mira Giri</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9813940809</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:25:58 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9813940809</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:25:58 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 04:04:04 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr"/>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Jana Marg 2 Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>9813940809@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>10:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>4d 38m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>4d 38m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 4:03 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343902</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Mira Giri</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Mira Giri</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9813940809</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:25:58 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9813940809</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:25:58 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 04:04:04 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Jana Marg 2 Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>9813940809@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>10:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>4d 38m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>4d 38m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 4:16 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow Internet   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346619</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Samikshya Basnet Shrestha</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Samikshya Basnet Shrestha</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9744476666</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 08:56:26 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9818079691</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 08:16:45 PM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 04:16:55 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.69475</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Near INSEC Nepal, Near LRI school, Near Makalu Petrol pump, Kalanki, Kathmandu , Bagmati, Central, N</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>sujitshrestha070@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.27792</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow Internet   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 20m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow Internet   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>52.8%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>6</v>
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -1071,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>7</v>
@@ -1083,7 +1083,7 @@
         <v>2</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX36"/>
+  <dimension ref="A1:AX37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7123,10 +7123,8 @@
           <t>Ramesh Bohora</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9851422020</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9851422020</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7216,10 +7214,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
@@ -7230,7 +7226,7 @@
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -7331,10 +7327,8 @@
           <t>Mira Giri</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9813940809</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9813940809</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7424,10 +7418,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
@@ -7438,7 +7430,7 @@
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -7539,10 +7531,8 @@
           <t>Mira Giri</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9813940809</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9813940809</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7632,10 +7622,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
@@ -7646,7 +7634,7 @@
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -7747,10 +7735,8 @@
           <t>Samikshya Basnet Shrestha</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9744476666</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9744476666</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7785,10 +7771,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.69475</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.69475</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7826,10 +7810,8 @@
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="AH36" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH36" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
@@ -7848,47 +7830,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.27792</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.27791999999999</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 20m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
           <t>Case : Slow Internet   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS36" s="3" t="inlineStr">
-        <is>
-          <t>1d 19h 20m</t>
-        </is>
-      </c>
-      <c r="AT36" s="3" t="inlineStr">
-        <is>
-          <t>1d 20h</t>
-        </is>
-      </c>
-      <c r="AU36" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV36" s="3" t="inlineStr">
-        <is>
-          <t>Case : Slow Internet   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -7897,6 +7875,214 @@
       <c r="AX36" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 4:24 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348583</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Rajendra Shrestha</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Rajendra Shrestha</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9860362753</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 04:24:46 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9762789289</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:34:52 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 04:24:46 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Birendra Chowk, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>9762789289@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Hareram Pandit</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>L36-2</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr"/>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>49m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>54.1%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.2%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.4%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.5%</t>
         </is>
       </c>
     </row>
@@ -853,13 +853,13 @@
         <v>6</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -1077,13 +1077,13 @@
         <v>7</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX37"/>
+  <dimension ref="A1:AX38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7935,20 +7935,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M37" s="3" t="inlineStr"/>
       <c r="N37" s="3" t="inlineStr">
         <is>
           <t>Rajendra Shrestha</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9860362753</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9860362753</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -8038,10 +8032,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
@@ -8052,37 +8044,253 @@
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>49m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS37" s="3" t="inlineStr">
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 4:43 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344035</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Nikita Upadhaya</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Nikita Upadhaya</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9818106969</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 04:43:21 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9841865344</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:10:05 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 04:43:21 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.67843</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>Near Advance oral dental hospital Saraswati Marga, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>neekitaupadhyay5@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>08:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.3465</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>49m</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>3d 23h 33m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV37" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW37" s="3" t="inlineStr">
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX37" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>46.5%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>4.7%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>51.2%</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX38"/>
+  <dimension ref="A1:AX44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -8145,10 +8145,8 @@
           <t>Nikita Upadhaya</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9818106969</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9818106969</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -8183,10 +8181,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>27.67843</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>27.67843</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -8242,47 +8238,43 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.3465</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.34650000000001</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>3d 23h 33m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>3d 23h 33m</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV38" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -8291,6 +8283,654 @@
       <c r="AX38" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 4:49 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr"/>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr"/>
+      <c r="V39" s="3" t="inlineStr"/>
+      <c r="W39" s="3" t="inlineStr"/>
+      <c r="X39" s="3" t="inlineStr"/>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr"/>
+      <c r="AA39" s="3" t="inlineStr"/>
+      <c r="AB39" s="3" t="inlineStr"/>
+      <c r="AC39" s="3" t="inlineStr"/>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr"/>
+      <c r="AF39" s="3" t="inlineStr"/>
+      <c r="AG39" s="3" t="inlineStr"/>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr"/>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr"/>
+      <c r="AM39" s="3" t="inlineStr"/>
+      <c r="AN39" s="3" t="inlineStr"/>
+      <c r="AO39" s="3" t="inlineStr"/>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 4:57 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr"/>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr"/>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr"/>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="3" t="inlineStr"/>
+      <c r="X40" s="3" t="inlineStr"/>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr"/>
+      <c r="AA40" s="3" t="inlineStr"/>
+      <c r="AB40" s="3" t="inlineStr"/>
+      <c r="AC40" s="3" t="inlineStr"/>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr"/>
+      <c r="AF40" s="3" t="inlineStr"/>
+      <c r="AG40" s="3" t="inlineStr"/>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr"/>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr"/>
+      <c r="AM40" s="3" t="inlineStr"/>
+      <c r="AN40" s="3" t="inlineStr"/>
+      <c r="AO40" s="3" t="inlineStr"/>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 5:01 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr"/>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr"/>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr"/>
+      <c r="V41" s="3" t="inlineStr"/>
+      <c r="W41" s="3" t="inlineStr"/>
+      <c r="X41" s="3" t="inlineStr"/>
+      <c r="Y41" s="3" t="inlineStr"/>
+      <c r="Z41" s="3" t="inlineStr"/>
+      <c r="AA41" s="3" t="inlineStr"/>
+      <c r="AB41" s="3" t="inlineStr"/>
+      <c r="AC41" s="3" t="inlineStr"/>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr"/>
+      <c r="AF41" s="3" t="inlineStr"/>
+      <c r="AG41" s="3" t="inlineStr"/>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr"/>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr"/>
+      <c r="AM41" s="3" t="inlineStr"/>
+      <c r="AN41" s="3" t="inlineStr"/>
+      <c r="AO41" s="3" t="inlineStr"/>
+      <c r="AP41" s="3" t="inlineStr"/>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 4:59 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="inlineStr"/>
+      <c r="O42" s="3" t="inlineStr"/>
+      <c r="P42" s="3" t="inlineStr"/>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr"/>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr"/>
+      <c r="V42" s="3" t="inlineStr"/>
+      <c r="W42" s="3" t="inlineStr"/>
+      <c r="X42" s="3" t="inlineStr"/>
+      <c r="Y42" s="3" t="inlineStr"/>
+      <c r="Z42" s="3" t="inlineStr"/>
+      <c r="AA42" s="3" t="inlineStr"/>
+      <c r="AB42" s="3" t="inlineStr"/>
+      <c r="AC42" s="3" t="inlineStr"/>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr"/>
+      <c r="AF42" s="3" t="inlineStr"/>
+      <c r="AG42" s="3" t="inlineStr"/>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr"/>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr"/>
+      <c r="AM42" s="3" t="inlineStr"/>
+      <c r="AN42" s="3" t="inlineStr"/>
+      <c r="AO42" s="3" t="inlineStr"/>
+      <c r="AP42" s="3" t="inlineStr"/>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 4:59 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr"/>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="inlineStr"/>
+      <c r="W43" s="3" t="inlineStr"/>
+      <c r="X43" s="3" t="inlineStr"/>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr"/>
+      <c r="AA43" s="3" t="inlineStr"/>
+      <c r="AB43" s="3" t="inlineStr"/>
+      <c r="AC43" s="3" t="inlineStr"/>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr"/>
+      <c r="AF43" s="3" t="inlineStr"/>
+      <c r="AG43" s="3" t="inlineStr"/>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr"/>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr"/>
+      <c r="AM43" s="3" t="inlineStr"/>
+      <c r="AN43" s="3" t="inlineStr"/>
+      <c r="AO43" s="3" t="inlineStr"/>
+      <c r="AP43" s="3" t="inlineStr"/>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 4:57 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
+      <c r="AA44" s="3" t="inlineStr"/>
+      <c r="AB44" s="3" t="inlineStr"/>
+      <c r="AC44" s="3" t="inlineStr"/>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr"/>
+      <c r="AF44" s="3" t="inlineStr"/>
+      <c r="AG44" s="3" t="inlineStr"/>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr"/>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr"/>
+      <c r="AM44" s="3" t="inlineStr"/>
+      <c r="AN44" s="3" t="inlineStr"/>
+      <c r="AO44" s="3" t="inlineStr"/>
+      <c r="AP44" s="3" t="inlineStr"/>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.7%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.5%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
     </row>
@@ -853,13 +853,13 @@
         <v>6</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -1077,13 +1077,13 @@
         <v>7</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX44"/>
+  <dimension ref="A1:AX45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -8934,6 +8934,214 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 5:16 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344924</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Saurav K.c</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Saurab K.c</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9869260369</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:16:03 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9869260369</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 02:53:20 PM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:16:03 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr"/>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>27.674485, 85.344945, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>sauravkc50@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>01:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr"/>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 22m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>48.9%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.4%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>5</v>
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -1074,7 +1074,7 @@
         <v>10</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>6</v>
@@ -1083,7 +1083,7 @@
         <v>2</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX45"/>
+  <dimension ref="A1:AX46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9001,10 +9001,8 @@
           <t>Saurab K.c</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9869260369</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9869260369</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -9094,10 +9092,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
@@ -9108,37 +9104,253 @@
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 22m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
           <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS45" s="3" t="inlineStr">
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 5:17 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348301</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Dhungana</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Dhungana</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9851139085</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:17:41 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9851139085</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:33:02 PM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:17:41 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>27.72001</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Jorpati, Kuwa tole, Near to New generation driving school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>dhunganasunil30@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>L61-5</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>85.37489</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>3d 2h 22m</t>
-        </is>
-      </c>
-      <c r="AU45" s="3" t="inlineStr">
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>4h 44m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV45" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW45" s="3" t="inlineStr">
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX45" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>51.1%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.8%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>6.4%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>7</v>
@@ -859,13 +859,13 @@
         <v>0</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -875,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>1</v>
@@ -893,7 +893,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -903,25 +903,25 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -934,13 +934,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>1</v>
@@ -1068,7 +1068,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>10</v>
@@ -1077,13 +1077,13 @@
         <v>8</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX46"/>
+  <dimension ref="A1:AX48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9205,10 +9205,8 @@
           <t>Sunil Dhungana</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9851139085</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9851139085</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9243,10 +9241,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>27.72001</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>27.72001</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -9302,55 +9298,475 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>L61-5</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>85.37489</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>85.37488999999999</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>4h 44m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS46" s="3" t="inlineStr">
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 5:37 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347020</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Raju Lama</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Raju Lama</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9848047877</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:37:49 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9848047877</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:34:04 AM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:37:49 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.67412</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Near Mount Hermoun School, Chyasal chowk , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr"/>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>09:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.32794</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT46" s="3" t="inlineStr">
-        <is>
-          <t>4h 44m</t>
-        </is>
-      </c>
-      <c r="AU46" s="3" t="inlineStr">
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>1d 7h 3m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV46" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW46" s="3" t="inlineStr">
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX46" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 5:40 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Iptv issue</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345715</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Pasina lama</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Pasina lama</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9867070773</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:40:46 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>BKT9867070773</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:13:28 AM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:40:46 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr"/>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Kausaltar, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>Abc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>19:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>L48-7</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr"/>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>2d 7h 27m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
@@ -850,7 +850,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>5</v>
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>2</v>
@@ -1074,7 +1074,7 @@
         <v>10</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>7</v>
@@ -1083,7 +1083,7 @@
         <v>2</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX48"/>
+  <dimension ref="A1:AX54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9413,10 +9413,8 @@
           <t>Raju Lama</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9848047877</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9848047877</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -9451,10 +9449,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>27.67412</t>
-        </is>
+      <c r="Y47" s="3" t="n">
+        <v>27.67412</v>
       </c>
       <c r="Z47" s="3" t="inlineStr">
         <is>
@@ -9506,25 +9502,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>2,8</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.32794</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.32794</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
@@ -9625,10 +9617,8 @@
           <t>Pasina lama</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9867070773</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9867070773</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -9700,10 +9690,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH48" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH48" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI48" s="3" t="inlineStr">
         <is>
@@ -9722,10 +9710,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
@@ -9736,37 +9722,1321 @@
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>2d 7h 27m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
           <t>Case : Iptv issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS48" s="3" t="inlineStr">
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 5:52 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348205</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Chetnath Dhimal</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Chetnath Dhimal</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9869190190</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:52:35 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9869190190</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 11:27:34 AM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:52:35 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr"/>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Lama Gas Station - Gas station Boudha Rd Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr"/>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>L52-2</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr"/>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>2d 7h 27m</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>6h 25m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV48" s="3" t="inlineStr">
-        <is>
-          <t>Case : Iptv issue  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW48" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX48" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 6:00 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 &amp; cctv   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 &amp; cctv</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345841</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Prasiddha Khakurel</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Prasiddha Khakurel</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9851090020</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:33:07 AM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9851090020</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:06:36 AM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 06:00:21 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.71434</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Thamel Dhobichaur near public youth campus, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>prasiddhakhakurel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>18:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>CDB163</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.30577</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 &amp; cctv   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 27m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 53m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 &amp; cctv   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 5:59 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 &amp; cctv   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 &amp; cctv</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345841</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Prasiddha Khakurel</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Prasiddha Khakurel</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9851090020</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:33:07 AM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9851090020</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:06:36 AM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 06:00:21 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>27.71434</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Thamel Dhobichaur near public youth campus, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>prasiddhakhakurel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>18:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>CDB163</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>85.30577</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 &amp; cctv   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 27m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 53m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 &amp; cctv   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 5:58 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 &amp; cctv   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 &amp; cctv</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345841</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Prasiddha Khakurel</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Prasiddha Khakurel</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9851090020</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:33:07 AM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>9851090020</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:06:36 AM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 06:00:21 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.71434</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Thamel Dhobichaur near public youth campus, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>prasiddhakhakurel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>18:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>CDB163</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.30577</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 &amp; cctv   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 27m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 53m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 &amp; cctv   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 5:57 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 &amp; cctv</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345841</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Prasiddha Khakurel</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Prasiddha Khakurel</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9851090020</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:33:07 AM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9851090020</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:06:36 AM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 06:00:21 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>27.71434</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Thamel Dhobichaur near public youth campus, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>prasiddhakhakurel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>18:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>CDB163</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>85.30577</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 27m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 53m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 5:56 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345565</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Maharjan</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Maharjan</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9841617523</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 08:50:36 AM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>9841617523</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 08:50:36 AM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:57:19 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr">
+        <is>
+          <t>27.71774</t>
+        </is>
+      </c>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>Near Prime College, Pahikwo Sadak, Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>mrznshyam@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr">
+        <is>
+          <t>20:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr">
+        <is>
+          <t>85.3018</t>
+        </is>
+      </c>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>2d 9h 6m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>2d 9h 6m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>58.2%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.5%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>58.2%</t>
         </is>
       </c>
     </row>
@@ -844,10 +844,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>8</v>
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1068,10 +1068,10 @@
         <v>4</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>9</v>
@@ -1083,7 +1083,7 @@
         <v>2</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX54"/>
+  <dimension ref="A1:AX56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9823,10 +9823,8 @@
           <t>Chetnath Dhimal</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9869190190</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9869190190</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -9912,10 +9910,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
@@ -9926,7 +9922,7 @@
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -10027,10 +10023,8 @@
           <t>Prasiddha Khakurel</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9851090020</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9851090020</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -10065,10 +10059,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.71434</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.71434</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -10124,25 +10116,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>CDB163</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.30577</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.30577</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 &amp; cctv   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
@@ -10243,10 +10231,8 @@
           <t>Prasiddha Khakurel</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9851090020</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9851090020</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10281,10 +10267,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y51" s="3" t="inlineStr">
-        <is>
-          <t>27.71434</t>
-        </is>
+      <c r="Y51" s="3" t="n">
+        <v>27.71434</v>
       </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
@@ -10340,25 +10324,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
           <t>CDB163</t>
         </is>
       </c>
-      <c r="AP51" s="3" t="inlineStr">
-        <is>
-          <t>85.30577</t>
-        </is>
+      <c r="AP51" s="3" t="n">
+        <v>85.30577</v>
       </c>
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 &amp; cctv   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
@@ -10459,10 +10439,8 @@
           <t>Prasiddha Khakurel</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9851090020</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9851090020</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -10497,10 +10475,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.71434</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.71434</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -10556,25 +10532,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>CDB163</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.30577</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.30577</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 &amp; cctv   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
@@ -10675,10 +10647,8 @@
           <t>Prasiddha Khakurel</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9851090020</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9851090020</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -10713,10 +10683,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y53" s="3" t="inlineStr">
-        <is>
-          <t>27.71434</t>
-        </is>
+      <c r="Y53" s="3" t="n">
+        <v>27.71434</v>
       </c>
       <c r="Z53" s="3" t="inlineStr">
         <is>
@@ -10772,25 +10740,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>CDB163</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>85.30577</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>85.30577</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -10891,10 +10855,8 @@
           <t>Shyam Maharjan</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9841617523</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9841617523</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -10929,10 +10891,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y54" s="3" t="inlineStr">
-        <is>
-          <t>27.71774</t>
-        </is>
+      <c r="Y54" s="3" t="n">
+        <v>27.71774</v>
       </c>
       <c r="Z54" s="3" t="inlineStr">
         <is>
@@ -10988,47 +10948,43 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="AP54" s="3" t="inlineStr">
-        <is>
-          <t>85.3018</t>
-        </is>
+      <c r="AP54" s="3" t="n">
+        <v>85.3018</v>
       </c>
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>2d 9h 6m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>2d 9h 6m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS54" s="3" t="inlineStr">
-        <is>
-          <t>2d 9h 6m</t>
-        </is>
-      </c>
-      <c r="AT54" s="3" t="inlineStr">
-        <is>
-          <t>2d 9h 6m</t>
-        </is>
-      </c>
-      <c r="AU54" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV54" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW54" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -11037,6 +10993,430 @@
       <c r="AX54" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 6:12 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347184</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Shrisha deula</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Shrisha deula</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9709290558</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 06:12:51 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>LTP9709290558</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:13:47 PM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 06:12:51 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr"/>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur Bangalamukhi, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>9709290558@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>07:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr"/>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>1d 5h 59m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX55" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 6:01 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348156</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Mahesh Thapa</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Mahesh Thapa</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9849485530</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 06:01:36 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>9849485530</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 11:03:27 AM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 06:01:36 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>27.711609</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Kageshwori,Manohara 6 Vidya arjan school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr">
+        <is>
+          <t>thapa92mahesh@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>L33-1</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>85.392886</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>6h 58m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Sep_2026.xlsx
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11063,10 +11063,8 @@
           <t>Shrisha deula</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9709290558</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9709290558</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -11156,10 +11154,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
@@ -11170,7 +11166,7 @@
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
@@ -11271,10 +11267,8 @@
           <t>Mahesh Thapa</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9849485530</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9849485530</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -11309,10 +11303,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y56" s="3" t="inlineStr">
-        <is>
-          <t>27.711609</t>
-        </is>
+      <c r="Y56" s="3" t="n">
+        <v>27.711609</v>
       </c>
       <c r="Z56" s="3" t="inlineStr">
         <is>
@@ -11368,25 +11360,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
           <t>L33-1</t>
         </is>
       </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>85.392886</t>
-        </is>
+      <c r="AP56" s="3" t="n">
+        <v>85.392886</v>
       </c>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
